--- a/Data/EXCEL/Transfer/salemon/202602/9941-salemon-202602.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202602/9941-salemon-202602.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202602\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AA86F3D-BF46-4BB5-AD42-9C0E0716F922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6657FF51-5711-4D28-A420-E282B89D6B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{97531502-FCE9-4140-AFA0-00DE2F8ED1C3}"/>
+    <workbookView xWindow="2790" yWindow="1560" windowWidth="20295" windowHeight="13320" xr2:uid="{55D36AFD-1CCA-457C-9956-690B9332345B}"/>
   </bookViews>
   <sheets>
     <sheet name="9941-salemon-202602" sheetId="2" r:id="rId1"/>
@@ -1258,7 +1258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E22699DA-B997-4BD4-94E0-13ED41C52EB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C30D49E-95E2-4D81-A376-ABA679FE1C6B}">
   <dimension ref="A1:Q244"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
